--- a/public/files/templates/Template_Mata_Kuliah.xlsx
+++ b/public/files/templates/Template_Mata_Kuliah.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP Victus\Desktop\Asesmen-CPL\public\files\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972A567A-EFD1-489B-9D76-B5B9DE768C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FAF177-5BDA-4774-9137-FDA78D199A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{73C2F049-E88D-49FE-A2DB-ABFCE865D333}"/>
   </bookViews>
@@ -38,13 +38,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Kode</t>
+    <t>Kode Mata Kuliah</t>
   </si>
   <si>
-    <t>Nama</t>
+    <t>Nama Mata Kuliah</t>
   </si>
   <si>
-    <t>Deskripsi</t>
+    <t>Deskripsi Mata Kuliah</t>
   </si>
 </sst>
 </file>
@@ -478,9 +478,9 @@
   <dimension ref="A1:E52"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="40.77734375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="130.77734375" style="10" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="47.88671875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="123.44140625" style="10" customWidth="1"/>
     <col min="4" max="4" width="10.5546875" style="2" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" hidden="1"/>
@@ -754,7 +754,7 @@
       <c r="C52" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7ZmxTtGMCVJSHnYlGyZLMbfl91Z6r6KJbbXIvZOQ+nzDHWNAjA13VuBh2D97QZkMPACreHKQphT193/MtG3ixg==" saltValue="VCAvHP/Pj7OlfIeKHsXwDA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jKtjfuU2dqDNESiceIZp6A7YFHlho98RjKoMDDBvW8IMaexjR8BgHKIAdXThTNE4qfJlUJx5yrueHd1gtZEpKA==" saltValue="K0gQOqoO4iau4fCGGTe+xg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="A2:C52" name="Range1"/>
   </protectedRanges>
